--- a/experiment/ELAN_bestx4/Test/results-Set5/Set5.xlsx
+++ b/experiment/ELAN_bestx4/Test/results-Set5/Set5.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33.69</v>
+        <v>33.72</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8934</v>
+        <v>0.8939</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.85</v>
+        <v>35</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9415</v>
+        <v>0.9429</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.73</v>
+        <v>28.83</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9195</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.99</v>
+        <v>33.01</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7984</v>
+        <v>0.7988</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.78</v>
+        <v>30.84</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9141</v>
+        <v>0.9149</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.21</v>
+        <v>32.28</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8934</v>
+        <v>0.8943</v>
       </c>
     </row>
   </sheetData>
